--- a/annotation/a558.xlsx
+++ b/annotation/a558.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,36 @@
           <t>id</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>kalima_text</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>num_sora</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sora_name_ar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>aya_no</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>kalima_text_emlaey</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -469,6 +499,30 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>يَٰٓأَيُّهَا</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>65</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ياأيها</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -489,6 +543,30 @@
       <c r="F3" t="n">
         <v>2</v>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ٱلنَّبِيُّ</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>65</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>النبي</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -509,6 +587,30 @@
       <c r="F4" t="n">
         <v>3</v>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>إِذَا</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>إذا</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -529,6 +631,30 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>طَلَّقۡتُمُ</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>65</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>طلقتم</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,6 +675,30 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ٱلنِّسَآءَ</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>65</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>النساء</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -569,6 +719,30 @@
       <c r="F7" t="n">
         <v>6</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>فَطَلِّقُوهُنَّ</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>65</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>فطلقوهن</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -589,6 +763,30 @@
       <c r="F8" t="n">
         <v>7</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>لِعِدَّتِهِنَّ</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>65</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>لعدتهن</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -609,6 +807,30 @@
       <c r="F9" t="n">
         <v>8</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وَأَحۡصُواْ</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>65</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>وأحصوا</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,6 +851,30 @@
       <c r="F10" t="n">
         <v>9</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ٱلۡعِدَّةَۖ</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>العدة</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -649,6 +895,30 @@
       <c r="F11" t="n">
         <v>10</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وَٱتَّقُواْ</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>65</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>واتقوا</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -669,6 +939,30 @@
       <c r="F12" t="n">
         <v>11</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ٱللَّهَ</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>65</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -689,6 +983,30 @@
       <c r="F13" t="n">
         <v>12</v>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>رَبَّكُمۡۖ</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>65</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ربكم</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -709,6 +1027,30 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>لَا</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>65</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -729,6 +1071,30 @@
       <c r="F15" t="n">
         <v>14</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>تُخۡرِجُوهُنَّ</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>65</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>تخرجوهن</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -749,6 +1115,30 @@
       <c r="F16" t="n">
         <v>15</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>مِنۢ</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>65</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>من</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -769,6 +1159,30 @@
       <c r="F17" t="n">
         <v>16</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>بُيُوتِهِنَّ</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>65</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>بيوتهن</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -789,6 +1203,30 @@
       <c r="F18" t="n">
         <v>17</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وَلَا</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>65</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ولا</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -809,6 +1247,30 @@
       <c r="F19" t="n">
         <v>18</v>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>يَخۡرُجۡنَ</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>65</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>يخرجن</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -829,6 +1291,30 @@
       <c r="F20" t="n">
         <v>19</v>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>إِلَّآ</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>65</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>إلا</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -849,6 +1335,30 @@
       <c r="F21" t="n">
         <v>20</v>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>أَن</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>65</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>أن</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -869,6 +1379,30 @@
       <c r="F22" t="n">
         <v>21</v>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>يَأۡتِينَ</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>65</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>يأتين</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -889,6 +1423,30 @@
       <c r="F23" t="n">
         <v>22</v>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>بِفَٰحِشَةٖ</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>65</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>بفاحشة</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -909,6 +1467,30 @@
       <c r="F24" t="n">
         <v>23</v>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>مُّبَيِّنَةٖۚ</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>65</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>مبينة</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -929,6 +1511,30 @@
       <c r="F25" t="n">
         <v>24</v>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وَتِلۡكَ</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>65</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>وتلك</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -949,6 +1555,30 @@
       <c r="F26" t="n">
         <v>25</v>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>حُدُودُ</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>65</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>حدود</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -969,6 +1599,30 @@
       <c r="F27" t="n">
         <v>26</v>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ٱللَّهِۚ</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>65</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -989,6 +1643,30 @@
       <c r="F28" t="n">
         <v>27</v>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وَمَن</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>65</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ومن</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1009,6 +1687,30 @@
       <c r="F29" t="n">
         <v>28</v>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>يَتَعَدَّ</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>65</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>يتعد</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1029,6 +1731,30 @@
       <c r="F30" t="n">
         <v>29</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>حُدُودَ</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>65</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>حدود</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1049,6 +1775,30 @@
       <c r="F31" t="n">
         <v>30</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ٱللَّهِ</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>65</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1069,6 +1819,30 @@
       <c r="F32" t="n">
         <v>31</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>فَقَدۡ</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>65</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>فقد</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1089,6 +1863,30 @@
       <c r="F33" t="n">
         <v>32</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ظَلَمَ</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>65</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ظلم</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1109,10 +1907,34 @@
       <c r="F34" t="n">
         <v>33</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>نَفۡسَهُۥۚ</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>65</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>نفسه</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>287.5757575757576</v>
+        <v>348.3369330453564</v>
       </c>
       <c r="B35" t="n">
         <v>266.5606060606061</v>
@@ -1127,18 +1949,42 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>34</v>
+        <v>135</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>لَا</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>65</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>245.5454545454546</v>
+        <v>287.5757575757576</v>
       </c>
       <c r="B36" t="n">
         <v>266.5606060606061</v>
       </c>
       <c r="C36" t="n">
-        <v>287.5757575757576</v>
+        <v>348.3369330453564</v>
       </c>
       <c r="D36" t="n">
         <v>319.6515151515152</v>
@@ -1147,18 +1993,42 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>35</v>
+        <v>134</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>تَدۡرِي</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>65</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>تدري</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>215.6818181818182</v>
+        <v>245.5454545454546</v>
       </c>
       <c r="B37" t="n">
         <v>266.5606060606061</v>
       </c>
       <c r="C37" t="n">
-        <v>245.5454545454546</v>
+        <v>287.5757575757576</v>
       </c>
       <c r="D37" t="n">
         <v>319.6515151515152</v>
@@ -1167,18 +2037,42 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>لَعَلَّ</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>65</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>لعل</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>154.8484848484849</v>
+        <v>215.6818181818182</v>
       </c>
       <c r="B38" t="n">
         <v>266.5606060606061</v>
       </c>
       <c r="C38" t="n">
-        <v>215.6818181818182</v>
+        <v>245.5454545454546</v>
       </c>
       <c r="D38" t="n">
         <v>319.6515151515152</v>
@@ -1187,18 +2081,42 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ٱللَّهَ</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>65</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120.5606060606061</v>
+        <v>154.8484848484849</v>
       </c>
       <c r="B39" t="n">
         <v>266.5606060606061</v>
       </c>
       <c r="C39" t="n">
-        <v>154.8484848484849</v>
+        <v>215.6818181818182</v>
       </c>
       <c r="D39" t="n">
         <v>319.6515151515152</v>
@@ -1207,18 +2125,42 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>يُحۡدِثُ</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>65</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>يحدث</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>78.53030303030305</v>
+        <v>120.5606060606061</v>
       </c>
       <c r="B40" t="n">
         <v>266.5606060606061</v>
       </c>
       <c r="C40" t="n">
-        <v>120.5606060606061</v>
+        <v>154.8484848484849</v>
       </c>
       <c r="D40" t="n">
         <v>319.6515151515152</v>
@@ -1227,18 +2169,42 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>بَعۡدَ</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>65</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>بعد</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>43.13636363636364</v>
+        <v>78.53030303030305</v>
       </c>
       <c r="B41" t="n">
         <v>266.5606060606061</v>
       </c>
       <c r="C41" t="n">
-        <v>78.53030303030305</v>
+        <v>120.5606060606061</v>
       </c>
       <c r="D41" t="n">
         <v>319.6515151515152</v>
@@ -1247,38 +2213,86 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ذَٰلِكَ</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>65</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ذلك</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>470.0757575757576</v>
+        <v>43.13636363636364</v>
       </c>
       <c r="B42" t="n">
+        <v>266.5606060606061</v>
+      </c>
+      <c r="C42" t="n">
+        <v>78.53030303030305</v>
+      </c>
+      <c r="D42" t="n">
         <v>319.6515151515152</v>
       </c>
-      <c r="C42" t="n">
-        <v>499.939393939394</v>
-      </c>
-      <c r="D42" t="n">
-        <v>372.7424242424243</v>
-      </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>أَمۡرٗا</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>65</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>أمرا</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>429.1515151515152</v>
+        <v>470.0757575757576</v>
       </c>
       <c r="B43" t="n">
         <v>319.6515151515152</v>
       </c>
       <c r="C43" t="n">
-        <v>470.0757575757576</v>
+        <v>499.939393939394</v>
       </c>
       <c r="D43" t="n">
         <v>372.7424242424243</v>
@@ -1287,18 +2301,42 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>فَإِذَا</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>65</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>فإذا</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>371.6363636363637</v>
+        <v>429.1515151515152</v>
       </c>
       <c r="B44" t="n">
         <v>319.6515151515152</v>
       </c>
       <c r="C44" t="n">
-        <v>429.1515151515152</v>
+        <v>470.0757575757576</v>
       </c>
       <c r="D44" t="n">
         <v>372.7424242424243</v>
@@ -1307,18 +2345,42 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>بَلَغۡنَ</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>65</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>بلغن</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>269.8787878787879</v>
+        <v>371.6363636363637</v>
       </c>
       <c r="B45" t="n">
         <v>319.6515151515152</v>
       </c>
       <c r="C45" t="n">
-        <v>371.6363636363637</v>
+        <v>429.1515151515152</v>
       </c>
       <c r="D45" t="n">
         <v>372.7424242424243</v>
@@ -1327,18 +2389,42 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>أَجَلَهُنَّ</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>65</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>أجلهن</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>188.0303030303031</v>
+        <v>269.8787878787879</v>
       </c>
       <c r="B46" t="n">
         <v>319.6515151515152</v>
       </c>
       <c r="C46" t="n">
-        <v>269.8787878787879</v>
+        <v>371.6363636363637</v>
       </c>
       <c r="D46" t="n">
         <v>372.7424242424243</v>
@@ -1347,18 +2433,42 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>فَأَمۡسِكُوهُنَّ</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>65</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>فأمسكوهن</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>169.2272727272727</v>
+        <v>188.0303030303031</v>
       </c>
       <c r="B47" t="n">
         <v>319.6515151515152</v>
       </c>
       <c r="C47" t="n">
-        <v>188.0303030303031</v>
+        <v>269.8787878787879</v>
       </c>
       <c r="D47" t="n">
         <v>372.7424242424243</v>
@@ -1367,18 +2477,42 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>بِمَعۡرُوفٍ</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>65</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>بمعروف</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>92.90909090909092</v>
+        <v>169.2272727272727</v>
       </c>
       <c r="B48" t="n">
         <v>319.6515151515152</v>
       </c>
       <c r="C48" t="n">
-        <v>169.2272727272727</v>
+        <v>188.0303030303031</v>
       </c>
       <c r="D48" t="n">
         <v>372.7424242424243</v>
@@ -1387,18 +2521,42 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>أَوۡ</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>65</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>أو</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6.636363636363637</v>
+        <v>92.90909090909092</v>
       </c>
       <c r="B49" t="n">
         <v>319.6515151515152</v>
       </c>
       <c r="C49" t="n">
-        <v>92.90909090909092</v>
+        <v>169.2272727272727</v>
       </c>
       <c r="D49" t="n">
         <v>372.7424242424243</v>
@@ -1407,38 +2565,86 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>فَارِقُوهُنَّ</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>65</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>فارقوهن</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>415.8787878787879</v>
+        <v>6.636363636363637</v>
       </c>
       <c r="B50" t="n">
+        <v>319.6515151515152</v>
+      </c>
+      <c r="C50" t="n">
+        <v>92.90909090909092</v>
+      </c>
+      <c r="D50" t="n">
         <v>372.7424242424243</v>
       </c>
-      <c r="C50" t="n">
-        <v>504.3636363636364</v>
-      </c>
-      <c r="D50" t="n">
-        <v>424.7272727272727</v>
-      </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>بِمَعۡرُوفٖ</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>65</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>بمعروف</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>368.3181818181819</v>
+        <v>415.8787878787879</v>
       </c>
       <c r="B51" t="n">
         <v>372.7424242424243</v>
       </c>
       <c r="C51" t="n">
-        <v>415.8787878787879</v>
+        <v>504.3636363636364</v>
       </c>
       <c r="D51" t="n">
         <v>424.7272727272727</v>
@@ -1447,18 +2653,42 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>50</v>
+        <v>49</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وَأَشۡهِدُواْ</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>65</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>وأشهدوا</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>324.0757575757576</v>
+        <v>368.3181818181819</v>
       </c>
       <c r="B52" t="n">
         <v>372.7424242424243</v>
       </c>
       <c r="C52" t="n">
-        <v>368.3181818181819</v>
+        <v>415.8787878787879</v>
       </c>
       <c r="D52" t="n">
         <v>424.7272727272727</v>
@@ -1467,18 +2697,42 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ذَوَيۡ</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>65</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ذوي</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>274.3030303030303</v>
+        <v>324.0757575757576</v>
       </c>
       <c r="B53" t="n">
         <v>372.7424242424243</v>
       </c>
       <c r="C53" t="n">
-        <v>324.0757575757576</v>
+        <v>368.3181818181819</v>
       </c>
       <c r="D53" t="n">
         <v>424.7272727272727</v>
@@ -1487,18 +2741,42 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>عَدۡلٖ</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>65</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>عدل</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>206.8333333333334</v>
+        <v>274.3030303030303</v>
       </c>
       <c r="B54" t="n">
         <v>372.7424242424243</v>
       </c>
       <c r="C54" t="n">
-        <v>274.3030303030303</v>
+        <v>324.0757575757576</v>
       </c>
       <c r="D54" t="n">
         <v>424.7272727272727</v>
@@ -1507,18 +2785,42 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>مِّنكُمۡ</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>65</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>منكم</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120.5606060606061</v>
+        <v>206.8333333333334</v>
       </c>
       <c r="B55" t="n">
         <v>372.7424242424243</v>
       </c>
       <c r="C55" t="n">
-        <v>206.8333333333334</v>
+        <v>274.3030303030303</v>
       </c>
       <c r="D55" t="n">
         <v>424.7272727272727</v>
@@ -1527,18 +2829,42 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وَأَقِيمُواْ</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>65</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>وأقيموا</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>95.12121212121214</v>
+        <v>120.5606060606061</v>
       </c>
       <c r="B56" t="n">
         <v>372.7424242424243</v>
       </c>
       <c r="C56" t="n">
-        <v>120.5606060606061</v>
+        <v>206.8333333333334</v>
       </c>
       <c r="D56" t="n">
         <v>424.7272727272727</v>
@@ -1547,18 +2873,42 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ٱلشَّهَٰدَةَ</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>65</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>الشهادة</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6.636363636363637</v>
+        <v>95.12121212121214</v>
       </c>
       <c r="B57" t="n">
         <v>372.7424242424243</v>
       </c>
       <c r="C57" t="n">
-        <v>95.12121212121214</v>
+        <v>120.5606060606061</v>
       </c>
       <c r="D57" t="n">
         <v>424.7272727272727</v>
@@ -1567,38 +2917,86 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>لِلَّهِۚ</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>65</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>لله</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>446.8484848484849</v>
+        <v>6.636363636363637</v>
       </c>
       <c r="B58" t="n">
+        <v>372.7424242424243</v>
+      </c>
+      <c r="C58" t="n">
+        <v>95.12121212121214</v>
+      </c>
+      <c r="D58" t="n">
         <v>424.7272727272727</v>
       </c>
-      <c r="C58" t="n">
-        <v>501.0454545454546</v>
-      </c>
-      <c r="D58" t="n">
-        <v>478.9242424242425</v>
-      </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ذَٰلِكُمۡ</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>65</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ذلكم</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>422.5151515151516</v>
+        <v>446.8484848484849</v>
       </c>
       <c r="B59" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C59" t="n">
-        <v>446.8484848484849</v>
+        <v>501.0454545454546</v>
       </c>
       <c r="D59" t="n">
         <v>478.9242424242425</v>
@@ -1607,18 +3005,42 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>58</v>
+        <v>57</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>يُوعَظُ</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>65</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>يوعظ</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>392.6515151515152</v>
+        <v>422.5151515151516</v>
       </c>
       <c r="B60" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C60" t="n">
-        <v>422.5151515151516</v>
+        <v>446.8484848484849</v>
       </c>
       <c r="D60" t="n">
         <v>478.9242424242425</v>
@@ -1627,18 +3049,42 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>بِهِۦ</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>65</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>به</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>360.5757575757576</v>
+        <v>392.6515151515152</v>
       </c>
       <c r="B61" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C61" t="n">
-        <v>392.6515151515152</v>
+        <v>422.5151515151516</v>
       </c>
       <c r="D61" t="n">
         <v>478.9242424242425</v>
@@ -1647,18 +3093,42 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>مَن</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>65</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>2</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>من</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>315.2272727272727</v>
+        <v>360.5757575757576</v>
       </c>
       <c r="B62" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C62" t="n">
-        <v>360.5757575757576</v>
+        <v>392.6515151515152</v>
       </c>
       <c r="D62" t="n">
         <v>478.9242424242425</v>
@@ -1667,18 +3137,42 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>61</v>
+        <v>60</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>كَانَ</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>65</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>2</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>كان</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>276.5151515151516</v>
+        <v>315.2272727272727</v>
       </c>
       <c r="B63" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C63" t="n">
-        <v>315.2272727272727</v>
+        <v>360.5757575757576</v>
       </c>
       <c r="D63" t="n">
         <v>478.9242424242425</v>
@@ -1687,18 +3181,42 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>يُؤۡمِنُ</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>65</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>يؤمن</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>216.7878787878788</v>
+        <v>276.5151515151516</v>
       </c>
       <c r="B64" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C64" t="n">
-        <v>276.5151515151516</v>
+        <v>315.2272727272727</v>
       </c>
       <c r="D64" t="n">
         <v>478.9242424242425</v>
@@ -1707,18 +3225,42 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>بِٱللَّهِ</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>65</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>بالله</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>165.9090909090909</v>
+        <v>216.7878787878788</v>
       </c>
       <c r="B65" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C65" t="n">
-        <v>216.7878787878788</v>
+        <v>276.5151515151516</v>
       </c>
       <c r="D65" t="n">
         <v>478.9242424242425</v>
@@ -1727,18 +3269,42 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وَٱلۡيَوۡمِ</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>65</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>واليوم</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127.1969696969697</v>
+        <v>165.9090909090909</v>
       </c>
       <c r="B66" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C66" t="n">
-        <v>165.9090909090909</v>
+        <v>216.7878787878788</v>
       </c>
       <c r="D66" t="n">
         <v>478.9242424242425</v>
@@ -1747,18 +3313,42 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>65</v>
+        <v>64</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ٱلۡأٓخِرِۚ</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>65</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>2</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>الآخر</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>88.4848484848485</v>
+        <v>127.1969696969697</v>
       </c>
       <c r="B67" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C67" t="n">
-        <v>127.1969696969697</v>
+        <v>165.9090909090909</v>
       </c>
       <c r="D67" t="n">
         <v>478.9242424242425</v>
@@ -1767,18 +3357,42 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وَمَن</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>65</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>2</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ومن</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>54.1969696969697</v>
+        <v>88.4848484848485</v>
       </c>
       <c r="B68" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C68" t="n">
-        <v>88.4848484848485</v>
+        <v>127.1969696969697</v>
       </c>
       <c r="D68" t="n">
         <v>478.9242424242425</v>
@@ -1787,18 +3401,42 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>يَتَّقِ</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>65</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>يتق</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>7.742424242424243</v>
+        <v>54.1969696969697</v>
       </c>
       <c r="B69" t="n">
         <v>424.7272727272727</v>
       </c>
       <c r="C69" t="n">
-        <v>54.1969696969697</v>
+        <v>88.4848484848485</v>
       </c>
       <c r="D69" t="n">
         <v>478.9242424242425</v>
@@ -1807,38 +3445,86 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ٱللَّهَ</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>65</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>481.1363636363637</v>
+        <v>7.742424242424243</v>
       </c>
       <c r="B70" t="n">
+        <v>424.7272727272727</v>
+      </c>
+      <c r="C70" t="n">
+        <v>54.1969696969697</v>
+      </c>
+      <c r="D70" t="n">
         <v>478.9242424242425</v>
       </c>
-      <c r="C70" t="n">
-        <v>503.2575757575758</v>
-      </c>
-      <c r="D70" t="n">
-        <v>530.909090909091</v>
-      </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>يَجۡعَل</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>65</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>يجعل</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>438.0000000000001</v>
+        <v>481.1363636363637</v>
       </c>
       <c r="B71" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C71" t="n">
-        <v>481.1363636363637</v>
+        <v>503.2575757575758</v>
       </c>
       <c r="D71" t="n">
         <v>530.909090909091</v>
@@ -1847,18 +3533,42 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>لَّهُۥ</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>65</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>له</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>347.3030303030304</v>
+        <v>438.0000000000001</v>
       </c>
       <c r="B72" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C72" t="n">
-        <v>402.6060606060607</v>
+        <v>481.1363636363637</v>
       </c>
       <c r="D72" t="n">
         <v>530.909090909091</v>
@@ -1867,18 +3577,42 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>72</v>
+        <v>70</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>مَخۡرَجٗا</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>65</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>مخرجا</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>324.0757575757576</v>
+        <v>347.3030303030304</v>
       </c>
       <c r="B73" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C73" t="n">
-        <v>347.3030303030304</v>
+        <v>402.6060606060607</v>
       </c>
       <c r="D73" t="n">
         <v>530.909090909091</v>
@@ -1887,18 +3621,42 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وَيَرۡزُقۡهُ</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>65</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ويرزقه</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>275.4090909090909</v>
+        <v>324.0757575757576</v>
       </c>
       <c r="B74" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C74" t="n">
-        <v>324.0757575757576</v>
+        <v>347.3030303030304</v>
       </c>
       <c r="D74" t="n">
         <v>530.909090909091</v>
@@ -1907,18 +3665,42 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>مِنۡ</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>65</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>من</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>257.7121212121212</v>
+        <v>275.4090909090909</v>
       </c>
       <c r="B75" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C75" t="n">
-        <v>275.4090909090909</v>
+        <v>324.0757575757576</v>
       </c>
       <c r="D75" t="n">
         <v>530.909090909091</v>
@@ -1927,18 +3709,42 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>حَيۡثُ</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>65</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>3</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>حيث</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>197.9848484848485</v>
+        <v>257.7121212121212</v>
       </c>
       <c r="B76" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C76" t="n">
-        <v>257.7121212121212</v>
+        <v>275.4090909090909</v>
       </c>
       <c r="D76" t="n">
         <v>530.909090909091</v>
@@ -1947,18 +3753,42 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>لَا</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>65</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>161.4848484848485</v>
+        <v>197.9848484848485</v>
       </c>
       <c r="B77" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C77" t="n">
-        <v>197.9848484848485</v>
+        <v>257.7121212121212</v>
       </c>
       <c r="D77" t="n">
         <v>530.909090909091</v>
@@ -1967,18 +3797,42 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>يَحۡتَسِبُۚ</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>65</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>يحتسب</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113.9242424242424</v>
+        <v>161.4848484848485</v>
       </c>
       <c r="B78" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C78" t="n">
-        <v>161.4848484848485</v>
+        <v>197.9848484848485</v>
       </c>
       <c r="D78" t="n">
         <v>530.909090909091</v>
@@ -1987,18 +3841,42 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وَمَن</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>65</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>3</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ومن</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>81.84848484848486</v>
+        <v>113.9242424242424</v>
       </c>
       <c r="B79" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C79" t="n">
-        <v>113.9242424242424</v>
+        <v>161.4848484848485</v>
       </c>
       <c r="D79" t="n">
         <v>530.909090909091</v>
@@ -2007,18 +3885,42 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>79</v>
+        <v>77</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>يَتَوَكَّلۡ</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>65</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>3</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>يتوكل</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>53.09090909090909</v>
+        <v>81.84848484848486</v>
       </c>
       <c r="B80" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C80" t="n">
-        <v>81.84848484848486</v>
+        <v>113.9242424242424</v>
       </c>
       <c r="D80" t="n">
         <v>530.909090909091</v>
@@ -2027,18 +3929,42 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>عَلَى</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>65</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>على</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>13.27272727272727</v>
+        <v>53.09090909090909</v>
       </c>
       <c r="B81" t="n">
         <v>478.9242424242425</v>
       </c>
       <c r="C81" t="n">
-        <v>53.09090909090909</v>
+        <v>81.84848484848486</v>
       </c>
       <c r="D81" t="n">
         <v>530.909090909091</v>
@@ -2047,38 +3973,86 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ٱللَّهِ</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>65</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>3</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>432.469696969697</v>
+        <v>13.27272727272727</v>
       </c>
       <c r="B82" t="n">
+        <v>478.9242424242425</v>
+      </c>
+      <c r="C82" t="n">
+        <v>53.09090909090909</v>
+      </c>
+      <c r="D82" t="n">
         <v>530.909090909091</v>
       </c>
-      <c r="C82" t="n">
-        <v>504.3636363636364</v>
-      </c>
-      <c r="D82" t="n">
-        <v>588.4242424242425</v>
-      </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>82</v>
+        <v>80</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>فَهُوَ</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>65</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>3</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>فهو</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>405.9242424242425</v>
+        <v>432.469696969697</v>
       </c>
       <c r="B83" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C83" t="n">
-        <v>432.469696969697</v>
+        <v>504.3636363636364</v>
       </c>
       <c r="D83" t="n">
         <v>588.4242424242425</v>
@@ -2087,18 +4061,42 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>حَسۡبُهُۥٓۚ</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>65</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>3</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>حسبه</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>369.4242424242425</v>
+        <v>405.9242424242425</v>
       </c>
       <c r="B84" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C84" t="n">
-        <v>405.9242424242425</v>
+        <v>432.469696969697</v>
       </c>
       <c r="D84" t="n">
         <v>588.4242424242425</v>
@@ -2107,18 +4105,42 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>إِنَّ</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>65</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>3</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>إن</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>331.8181818181819</v>
+        <v>369.4242424242425</v>
       </c>
       <c r="B85" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C85" t="n">
-        <v>369.4242424242425</v>
+        <v>405.9242424242425</v>
       </c>
       <c r="D85" t="n">
         <v>588.4242424242425</v>
@@ -2127,18 +4149,42 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>85</v>
+        <v>83</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ٱللَّهَ</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>65</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>285.3636363636364</v>
+        <v>331.8181818181819</v>
       </c>
       <c r="B86" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C86" t="n">
-        <v>331.8181818181819</v>
+        <v>369.4242424242425</v>
       </c>
       <c r="D86" t="n">
         <v>588.4242424242425</v>
@@ -2147,18 +4193,42 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>بَٰلِغُ</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>65</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>3</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>بالغ</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>257.7121212121212</v>
+        <v>285.3636363636364</v>
       </c>
       <c r="B87" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C87" t="n">
-        <v>285.3636363636364</v>
+        <v>331.8181818181819</v>
       </c>
       <c r="D87" t="n">
         <v>588.4242424242425</v>
@@ -2167,18 +4237,42 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>87</v>
+        <v>85</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>أَمۡرِهِۦۚ</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>65</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>أمره</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>205.7272727272727</v>
+        <v>257.7121212121212</v>
       </c>
       <c r="B88" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C88" t="n">
-        <v>257.7121212121212</v>
+        <v>285.3636363636364</v>
       </c>
       <c r="D88" t="n">
         <v>588.4242424242425</v>
@@ -2187,18 +4281,42 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>88</v>
+        <v>86</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>قَدۡ</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>65</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>قد</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>174.7575757575758</v>
+        <v>205.7272727272727</v>
       </c>
       <c r="B89" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C89" t="n">
-        <v>205.7272727272727</v>
+        <v>257.7121212121212</v>
       </c>
       <c r="D89" t="n">
         <v>588.4242424242425</v>
@@ -2207,18 +4325,42 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>89</v>
+        <v>87</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>جَعَلَ</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>65</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>3</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>جعل</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132.7272727272727</v>
+        <v>174.7575757575758</v>
       </c>
       <c r="B90" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C90" t="n">
-        <v>174.7575757575758</v>
+        <v>205.7272727272727</v>
       </c>
       <c r="D90" t="n">
         <v>588.4242424242425</v>
@@ -2227,18 +4369,42 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>90</v>
+        <v>88</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ٱللَّهُ</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>65</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>3</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>87.37878787878789</v>
+        <v>132.7272727272727</v>
       </c>
       <c r="B91" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C91" t="n">
-        <v>132.7272727272727</v>
+        <v>174.7575757575758</v>
       </c>
       <c r="D91" t="n">
         <v>588.4242424242425</v>
@@ -2247,18 +4413,42 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>91</v>
+        <v>89</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>لِكُلِّ</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>65</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>لكل</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>45.34848484848485</v>
+        <v>87.37878787878789</v>
       </c>
       <c r="B92" t="n">
         <v>530.909090909091</v>
       </c>
       <c r="C92" t="n">
-        <v>87.37878787878789</v>
+        <v>132.7272727272727</v>
       </c>
       <c r="D92" t="n">
         <v>588.4242424242425</v>
@@ -2267,38 +4457,86 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>92</v>
+        <v>90</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>شَيۡءٖ</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>65</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>3</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>شيء</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>453.4848484848486</v>
+        <v>45.34848484848485</v>
       </c>
       <c r="B93" t="n">
+        <v>530.909090909091</v>
+      </c>
+      <c r="C93" t="n">
+        <v>87.37878787878789</v>
+      </c>
+      <c r="D93" t="n">
         <v>588.4242424242425</v>
       </c>
-      <c r="C93" t="n">
-        <v>503.2575757575758</v>
-      </c>
-      <c r="D93" t="n">
-        <v>640.409090909091</v>
-      </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>قَدۡرٗا</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>65</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>3</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>قدرا</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>402.6060606060607</v>
+        <v>453.4848484848486</v>
       </c>
       <c r="B94" t="n">
         <v>588.4242424242425</v>
       </c>
       <c r="C94" t="n">
-        <v>453.4848484848486</v>
+        <v>503.2575757575758</v>
       </c>
       <c r="D94" t="n">
         <v>640.409090909091</v>
@@ -2307,18 +4545,42 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وَٱلَّٰٓـِٔي</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>65</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>4</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>واللائي</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>369.4242424242425</v>
+        <v>402.6060606060607</v>
       </c>
       <c r="B95" t="n">
         <v>588.4242424242425</v>
       </c>
       <c r="C95" t="n">
-        <v>402.6060606060607</v>
+        <v>453.4848484848486</v>
       </c>
       <c r="D95" t="n">
         <v>640.409090909091</v>
@@ -2327,18 +4589,42 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>95</v>
+        <v>93</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>يَئِسۡنَ</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>65</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>يئسن</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>287.5757575757576</v>
+        <v>369.4242424242425</v>
       </c>
       <c r="B96" t="n">
         <v>588.4242424242425</v>
       </c>
       <c r="C96" t="n">
-        <v>369.4242424242425</v>
+        <v>402.6060606060607</v>
       </c>
       <c r="D96" t="n">
         <v>640.409090909091</v>
@@ -2347,18 +4633,42 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>96</v>
+        <v>94</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>مِنَ</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>65</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>4</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>من</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>255.5</v>
+        <v>287.5757575757576</v>
       </c>
       <c r="B97" t="n">
         <v>588.4242424242425</v>
       </c>
       <c r="C97" t="n">
-        <v>287.5757575757576</v>
+        <v>369.4242424242425</v>
       </c>
       <c r="D97" t="n">
         <v>640.409090909091</v>
@@ -2367,18 +4677,42 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>97</v>
+        <v>95</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ٱلۡمَحِيضِ</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>65</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>4</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>المحيض</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>181.3939393939394</v>
+        <v>255.5</v>
       </c>
       <c r="B98" t="n">
         <v>588.4242424242425</v>
       </c>
       <c r="C98" t="n">
-        <v>255.5</v>
+        <v>287.5757575757576</v>
       </c>
       <c r="D98" t="n">
         <v>640.409090909091</v>
@@ -2387,18 +4721,42 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>98</v>
+        <v>96</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>مِن</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>65</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>4</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>من</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>154.8484848484849</v>
+        <v>181.3939393939394</v>
       </c>
       <c r="B99" t="n">
         <v>588.4242424242425</v>
       </c>
       <c r="C99" t="n">
-        <v>181.3939393939394</v>
+        <v>255.5</v>
       </c>
       <c r="D99" t="n">
         <v>640.409090909091</v>
@@ -2407,18 +4765,42 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>99</v>
+        <v>97</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>نِّسَآئِكُمۡ</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>65</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>نسائكم</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>90.6969696969697</v>
+        <v>154.8484848484849</v>
       </c>
       <c r="B100" t="n">
         <v>588.4242424242425</v>
       </c>
       <c r="C100" t="n">
-        <v>154.8484848484849</v>
+        <v>181.3939393939394</v>
       </c>
       <c r="D100" t="n">
         <v>640.409090909091</v>
@@ -2427,18 +4809,42 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>100</v>
+        <v>98</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>إِنِ</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>65</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>إن</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>7.742424242424243</v>
+        <v>90.6969696969697</v>
       </c>
       <c r="B101" t="n">
         <v>588.4242424242425</v>
       </c>
       <c r="C101" t="n">
-        <v>90.6969696969697</v>
+        <v>154.8484848484849</v>
       </c>
       <c r="D101" t="n">
         <v>640.409090909091</v>
@@ -2447,38 +4853,86 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ٱرۡتَبۡتُمۡ</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>65</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>ارتبتم</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>452.3787878787879</v>
+        <v>7.742424242424243</v>
       </c>
       <c r="B102" t="n">
+        <v>588.4242424242425</v>
+      </c>
+      <c r="C102" t="n">
+        <v>90.6969696969697</v>
+      </c>
+      <c r="D102" t="n">
         <v>640.409090909091</v>
       </c>
-      <c r="C102" t="n">
-        <v>503.2575757575758</v>
-      </c>
-      <c r="D102" t="n">
-        <v>697.9242424242425</v>
-      </c>
       <c r="E102" t="b">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>102</v>
+        <v>100</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>فَعِدَّتُهُنَّ</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>65</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>4</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>فعدتهن</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>394.8636363636364</v>
+        <v>452.3787878787879</v>
       </c>
       <c r="B103" t="n">
         <v>640.409090909091</v>
       </c>
       <c r="C103" t="n">
-        <v>452.3787878787879</v>
+        <v>503.2575757575758</v>
       </c>
       <c r="D103" t="n">
         <v>697.9242424242425</v>
@@ -2487,18 +4941,42 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>103</v>
+        <v>101</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ثَلَٰثَةُ</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>65</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>4</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>ثلاثة</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>355.0454545454546</v>
+        <v>394.8636363636364</v>
       </c>
       <c r="B104" t="n">
         <v>640.409090909091</v>
       </c>
       <c r="C104" t="n">
-        <v>394.8636363636364</v>
+        <v>452.3787878787879</v>
       </c>
       <c r="D104" t="n">
         <v>697.9242424242425</v>
@@ -2507,18 +4985,42 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>أَشۡهُرٖ</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>65</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>4</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>أشهر</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>339.5606060606061</v>
+        <v>355.0454545454546</v>
       </c>
       <c r="B105" t="n">
         <v>640.409090909091</v>
       </c>
       <c r="C105" t="n">
-        <v>355.0454545454546</v>
+        <v>394.8636363636364</v>
       </c>
       <c r="D105" t="n">
         <v>697.9242424242425</v>
@@ -2527,18 +5029,42 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>106</v>
+        <v>103</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>وَٱلَّٰٓـِٔي</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>65</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>4</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>واللائي</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>283.1515151515152</v>
+        <v>339.5606060606061</v>
       </c>
       <c r="B106" t="n">
         <v>640.409090909091</v>
       </c>
       <c r="C106" t="n">
-        <v>339.5606060606061</v>
+        <v>355.0454545454546</v>
       </c>
       <c r="D106" t="n">
         <v>697.9242424242425</v>
@@ -2547,18 +5073,42 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>107</v>
+        <v>104</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>لَمۡ</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>65</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>4</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>لم</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>216.7878787878788</v>
+        <v>283.1515151515152</v>
       </c>
       <c r="B107" t="n">
         <v>640.409090909091</v>
       </c>
       <c r="C107" t="n">
-        <v>283.1515151515152</v>
+        <v>339.5606060606061</v>
       </c>
       <c r="D107" t="n">
         <v>697.9242424242425</v>
@@ -2567,18 +5117,42 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>يَحِضۡنَۚ</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>65</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>4</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>يحضن</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>150.4242424242424</v>
+        <v>216.7878787878788</v>
       </c>
       <c r="B108" t="n">
         <v>640.409090909091</v>
       </c>
       <c r="C108" t="n">
-        <v>216.7878787878788</v>
+        <v>283.1515151515152</v>
       </c>
       <c r="D108" t="n">
         <v>697.9242424242425</v>
@@ -2587,18 +5161,42 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>109</v>
+        <v>106</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>وَأُوْلَٰتُ</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>65</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>4</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>وأولات</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>89.59090909090911</v>
+        <v>150.4242424242424</v>
       </c>
       <c r="B109" t="n">
         <v>640.409090909091</v>
       </c>
       <c r="C109" t="n">
-        <v>150.4242424242424</v>
+        <v>216.7878787878788</v>
       </c>
       <c r="D109" t="n">
         <v>697.9242424242425</v>
@@ -2607,18 +5205,42 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>110</v>
+        <v>107</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ٱلۡأَحۡمَالِ</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>65</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>4</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>الأحمال</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>68.57575757575758</v>
+        <v>89.59090909090911</v>
       </c>
       <c r="B110" t="n">
         <v>640.409090909091</v>
       </c>
       <c r="C110" t="n">
-        <v>89.59090909090911</v>
+        <v>150.4242424242424</v>
       </c>
       <c r="D110" t="n">
         <v>697.9242424242425</v>
@@ -2627,18 +5249,42 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>111</v>
+        <v>108</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>أَجَلُهُنَّ</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>65</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>4</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>أجلهن</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>8.84848484848485</v>
+        <v>68.57575757575758</v>
       </c>
       <c r="B111" t="n">
         <v>640.409090909091</v>
       </c>
       <c r="C111" t="n">
-        <v>68.57575757575758</v>
+        <v>89.59090909090911</v>
       </c>
       <c r="D111" t="n">
         <v>697.9242424242425</v>
@@ -2647,38 +5293,86 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>112</v>
+        <v>109</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>أَن</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>65</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>4</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>أن</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>434.6818181818182</v>
+        <v>8.84848484848485</v>
       </c>
       <c r="B112" t="n">
+        <v>640.409090909091</v>
+      </c>
+      <c r="C112" t="n">
+        <v>68.57575757575758</v>
+      </c>
+      <c r="D112" t="n">
         <v>697.9242424242425</v>
       </c>
-      <c r="C112" t="n">
-        <v>503.2575757575758</v>
-      </c>
-      <c r="D112" t="n">
-        <v>744.378787878788</v>
-      </c>
       <c r="E112" t="b">
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>113</v>
+        <v>110</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>يَضَعۡنَ</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>65</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>4</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>يضعن</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>397.0757575757576</v>
+        <v>434.6818181818182</v>
       </c>
       <c r="B113" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C113" t="n">
-        <v>434.6818181818182</v>
+        <v>503.2575757575758</v>
       </c>
       <c r="D113" t="n">
         <v>744.378787878788</v>
@@ -2687,18 +5381,42 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>114</v>
+        <v>111</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>حَمۡلَهُنَّۚ</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>65</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>4</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>حملهن</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>361.6818181818182</v>
+        <v>397.0757575757576</v>
       </c>
       <c r="B114" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C114" t="n">
-        <v>397.0757575757576</v>
+        <v>434.6818181818182</v>
       </c>
       <c r="D114" t="n">
         <v>744.378787878788</v>
@@ -2707,18 +5425,42 @@
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>115</v>
+        <v>112</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>وَمَن</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>65</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>4</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>ومن</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>330.7121212121212</v>
+        <v>361.6818181818182</v>
       </c>
       <c r="B115" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C115" t="n">
-        <v>361.6818181818182</v>
+        <v>397.0757575757576</v>
       </c>
       <c r="D115" t="n">
         <v>744.378787878788</v>
@@ -2727,18 +5469,42 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>116</v>
+        <v>113</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>يَتَّقِ</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>65</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>4</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>يتق</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>279.8333333333334</v>
+        <v>330.7121212121212</v>
       </c>
       <c r="B116" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C116" t="n">
-        <v>330.7121212121212</v>
+        <v>361.6818181818182</v>
       </c>
       <c r="D116" t="n">
         <v>744.378787878788</v>
@@ -2747,18 +5513,42 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>117</v>
+        <v>114</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>ٱللَّهَ</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>65</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>4</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>257.7121212121212</v>
+        <v>279.8333333333334</v>
       </c>
       <c r="B117" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C117" t="n">
-        <v>279.8333333333334</v>
+        <v>330.7121212121212</v>
       </c>
       <c r="D117" t="n">
         <v>744.378787878788</v>
@@ -2767,18 +5557,42 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>118</v>
+        <v>115</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>يَجۡعَل</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>65</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>4</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>يجعل</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>227.8484848484849</v>
+        <v>257.7121212121212</v>
       </c>
       <c r="B118" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C118" t="n">
-        <v>257.7121212121212</v>
+        <v>279.8333333333334</v>
       </c>
       <c r="D118" t="n">
         <v>744.378787878788</v>
@@ -2787,18 +5601,42 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>لَّهُۥ</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>65</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>4</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>له</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>183.6060606060606</v>
+        <v>227.8484848484849</v>
       </c>
       <c r="B119" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C119" t="n">
-        <v>227.8484848484849</v>
+        <v>257.7121212121212</v>
       </c>
       <c r="D119" t="n">
         <v>744.378787878788</v>
@@ -2807,18 +5645,42 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>120</v>
+        <v>117</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>مِنۡ</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>65</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>4</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>من</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>144.8939393939394</v>
+        <v>183.6060606060606</v>
       </c>
       <c r="B120" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C120" t="n">
-        <v>183.6060606060606</v>
+        <v>227.8484848484849</v>
       </c>
       <c r="D120" t="n">
         <v>744.378787878788</v>
@@ -2827,18 +5689,42 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>121</v>
+        <v>118</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>أَمۡرِهِۦ</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>65</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>4</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>أمره</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>68.57575757575758</v>
+        <v>144.8939393939394</v>
       </c>
       <c r="B121" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C121" t="n">
-        <v>111.7121212121212</v>
+        <v>183.6060606060606</v>
       </c>
       <c r="D121" t="n">
         <v>744.378787878788</v>
@@ -2847,18 +5733,42 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>123</v>
+        <v>119</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>يُسۡرٗا</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>65</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>4</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>يسرا</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>40.92424242424243</v>
+        <v>68.57575757575758</v>
       </c>
       <c r="B122" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C122" t="n">
-        <v>68.57575757575758</v>
+        <v>111.7121212121212</v>
       </c>
       <c r="D122" t="n">
         <v>744.378787878788</v>
@@ -2867,18 +5777,42 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>124</v>
+        <v>120</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ذَٰلِكَ</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>65</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>5</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>ذلك</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>7.742424242424243</v>
+        <v>40.92424242424243</v>
       </c>
       <c r="B123" t="n">
         <v>697.9242424242425</v>
       </c>
       <c r="C123" t="n">
-        <v>40.92424242424243</v>
+        <v>68.57575757575758</v>
       </c>
       <c r="D123" t="n">
         <v>744.378787878788</v>
@@ -2887,38 +5821,86 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>125</v>
+        <v>121</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>أَمۡرُ</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>65</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>5</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>أمر</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>459.0151515151516</v>
+        <v>7.742424242424243</v>
       </c>
       <c r="B124" t="n">
+        <v>697.9242424242425</v>
+      </c>
+      <c r="C124" t="n">
+        <v>40.92424242424243</v>
+      </c>
+      <c r="D124" t="n">
         <v>744.378787878788</v>
       </c>
-      <c r="C124" t="n">
-        <v>503.2575757575758</v>
-      </c>
-      <c r="D124" t="n">
-        <v>801.8939393939395</v>
-      </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>126</v>
+        <v>122</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ٱللَّهِ</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>65</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>5</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>412.5606060606061</v>
+        <v>459.0151515151516</v>
       </c>
       <c r="B125" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C125" t="n">
-        <v>459.0151515151516</v>
+        <v>503.2575757575758</v>
       </c>
       <c r="D125" t="n">
         <v>801.8939393939395</v>
@@ -2927,18 +5909,42 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>127</v>
+        <v>123</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>أَنزَلَهُۥٓ</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>65</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>5</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>أنزله</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>373.8484848484849</v>
+        <v>412.5606060606061</v>
       </c>
       <c r="B126" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C126" t="n">
-        <v>412.5606060606061</v>
+        <v>459.0151515151516</v>
       </c>
       <c r="D126" t="n">
         <v>801.8939393939395</v>
@@ -2947,18 +5953,42 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>128</v>
+        <v>124</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>إِلَيۡكُمۡۚ</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>65</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>5</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>إليكم</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>338.4545454545455</v>
+        <v>373.8484848484849</v>
       </c>
       <c r="B127" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C127" t="n">
-        <v>373.8484848484849</v>
+        <v>412.5606060606061</v>
       </c>
       <c r="D127" t="n">
         <v>801.8939393939395</v>
@@ -2967,18 +5997,42 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>129</v>
+        <v>125</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>وَمَن</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>65</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>5</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>ومن</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>307.4848484848485</v>
+        <v>338.4545454545455</v>
       </c>
       <c r="B128" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C128" t="n">
-        <v>338.4545454545455</v>
+        <v>373.8484848484849</v>
       </c>
       <c r="D128" t="n">
         <v>801.8939393939395</v>
@@ -2987,18 +6041,42 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>130</v>
+        <v>126</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>يَتَّقِ</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>65</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>5</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>يتق</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>266.5606060606061</v>
+        <v>307.4848484848485</v>
       </c>
       <c r="B129" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C129" t="n">
-        <v>307.4848484848485</v>
+        <v>338.4545454545455</v>
       </c>
       <c r="D129" t="n">
         <v>801.8939393939395</v>
@@ -3007,18 +6085,42 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>131</v>
+        <v>127</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>ٱللَّهَ</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>65</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>5</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>الله</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>236.6969696969697</v>
+        <v>266.5606060606061</v>
       </c>
       <c r="B130" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C130" t="n">
-        <v>266.5606060606061</v>
+        <v>307.4848484848485</v>
       </c>
       <c r="D130" t="n">
         <v>801.8939393939395</v>
@@ -3027,18 +6129,42 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>132</v>
+        <v>128</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>يُكَفِّرۡ</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>65</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>5</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>يكفر</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>168.1212121212122</v>
+        <v>236.6969696969697</v>
       </c>
       <c r="B131" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C131" t="n">
-        <v>236.6969696969697</v>
+        <v>266.5606060606061</v>
       </c>
       <c r="D131" t="n">
         <v>801.8939393939395</v>
@@ -3047,18 +6173,42 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>133</v>
+        <v>129</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>عَنۡهُ</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>65</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>5</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>عنه</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>106.1818181818182</v>
+        <v>168.1212121212122</v>
       </c>
       <c r="B132" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C132" t="n">
-        <v>168.1212121212122</v>
+        <v>236.6969696969697</v>
       </c>
       <c r="D132" t="n">
         <v>801.8939393939395</v>
@@ -3067,18 +6217,42 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>134</v>
+        <v>130</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>سَيِّـَٔاتِهِۦ</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>65</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>5</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>سيئاته</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>81.84848484848486</v>
+        <v>106.1818181818182</v>
       </c>
       <c r="B133" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C133" t="n">
-        <v>106.1818181818182</v>
+        <v>168.1212121212122</v>
       </c>
       <c r="D133" t="n">
         <v>801.8939393939395</v>
@@ -3087,18 +6261,42 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>135</v>
+        <v>131</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>وَيُعۡظِمۡ</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>65</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>5</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>ويعظم</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>46.45454545454546</v>
+        <v>81.84848484848486</v>
       </c>
       <c r="B134" t="n">
         <v>744.378787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>81.84848484848486</v>
+        <v>106.1818181818182</v>
       </c>
       <c r="D134" t="n">
         <v>801.8939393939395</v>
@@ -3107,7 +6305,75 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>136</v>
+        <v>132</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>لَهُۥٓ</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>65</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>5</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>له</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>46.45454545454546</v>
+      </c>
+      <c r="B135" t="n">
+        <v>744.378787878788</v>
+      </c>
+      <c r="C135" t="n">
+        <v>81.84848484848486</v>
+      </c>
+      <c r="D135" t="n">
+        <v>801.8939393939395</v>
+      </c>
+      <c r="E135" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>133</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>أَجۡرًا</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>65</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>الطَّلَاق</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>5</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>أجرا</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3212,7 +6478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4301,79 +7567,79 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>355.0454545454546</v>
+        <v>348.3369330453564</v>
       </c>
       <c r="B99" t="n">
-        <v>640.409090909091</v>
+        <v>266.5606060606061</v>
       </c>
       <c r="C99" t="n">
-        <v>697.9242424242425</v>
+        <v>319.6515151515152</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>359.469696969697</v>
+        <v>355.0454545454546</v>
       </c>
       <c r="B100" t="n">
-        <v>159.2727272727273</v>
+        <v>640.409090909091</v>
       </c>
       <c r="C100" t="n">
-        <v>214.5757575757576</v>
+        <v>697.9242424242425</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>360.5757575757576</v>
+        <v>359.469696969697</v>
       </c>
       <c r="B101" t="n">
-        <v>424.7272727272727</v>
+        <v>159.2727272727273</v>
       </c>
       <c r="C101" t="n">
-        <v>478.9242424242425</v>
+        <v>214.5757575757576</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>361.6818181818182</v>
+        <v>360.5757575757576</v>
       </c>
       <c r="B102" t="n">
-        <v>697.9242424242425</v>
+        <v>424.7272727272727</v>
       </c>
       <c r="C102" t="n">
-        <v>744.378787878788</v>
+        <v>478.9242424242425</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>363.8939393939394</v>
+        <v>361.6818181818182</v>
       </c>
       <c r="B103" t="n">
-        <v>266.5606060606061</v>
+        <v>697.9242424242425</v>
       </c>
       <c r="C103" t="n">
-        <v>319.6515151515152</v>
+        <v>744.378787878788</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>368.3181818181819</v>
+        <v>363.8939393939394</v>
       </c>
       <c r="B104" t="n">
-        <v>372.7424242424243</v>
+        <v>266.5606060606061</v>
       </c>
       <c r="C104" t="n">
-        <v>424.7272727272727</v>
+        <v>319.6515151515152</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>369.4242424242425</v>
+        <v>368.3181818181819</v>
       </c>
       <c r="B105" t="n">
-        <v>109.5</v>
+        <v>372.7424242424243</v>
       </c>
       <c r="C105" t="n">
-        <v>159.2727272727273</v>
+        <v>424.7272727272727</v>
       </c>
     </row>
     <row r="106">
@@ -4381,10 +7647,10 @@
         <v>369.4242424242425</v>
       </c>
       <c r="B106" t="n">
-        <v>530.909090909091</v>
+        <v>109.5</v>
       </c>
       <c r="C106" t="n">
-        <v>588.4242424242425</v>
+        <v>159.2727272727273</v>
       </c>
     </row>
     <row r="107">
@@ -4392,98 +7658,98 @@
         <v>369.4242424242425</v>
       </c>
       <c r="B107" t="n">
+        <v>530.909090909091</v>
+      </c>
+      <c r="C107" t="n">
         <v>588.4242424242425</v>
-      </c>
-      <c r="C107" t="n">
-        <v>640.409090909091</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>371.6363636363637</v>
+        <v>369.4242424242425</v>
       </c>
       <c r="B108" t="n">
-        <v>319.6515151515152</v>
+        <v>588.4242424242425</v>
       </c>
       <c r="C108" t="n">
-        <v>372.7424242424243</v>
+        <v>640.409090909091</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>373.8484848484849</v>
+        <v>371.6363636363637</v>
       </c>
       <c r="B109" t="n">
-        <v>744.378787878788</v>
+        <v>319.6515151515152</v>
       </c>
       <c r="C109" t="n">
-        <v>801.8939393939395</v>
+        <v>372.7424242424243</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>374.9545454545455</v>
+        <v>373.8484848484849</v>
       </c>
       <c r="B110" t="n">
-        <v>214.5757575757576</v>
+        <v>744.378787878788</v>
       </c>
       <c r="C110" t="n">
-        <v>266.5606060606061</v>
+        <v>801.8939393939395</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>388.2272727272727</v>
+        <v>374.9545454545455</v>
       </c>
       <c r="B111" t="n">
-        <v>109.5</v>
+        <v>214.5757575757576</v>
       </c>
       <c r="C111" t="n">
-        <v>159.2727272727273</v>
+        <v>266.5606060606061</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>392.6515151515152</v>
+        <v>388.2272727272727</v>
       </c>
       <c r="B112" t="n">
-        <v>424.7272727272727</v>
+        <v>109.5</v>
       </c>
       <c r="C112" t="n">
-        <v>478.9242424242425</v>
+        <v>159.2727272727273</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>394.8636363636364</v>
+        <v>392.6515151515152</v>
       </c>
       <c r="B113" t="n">
-        <v>640.409090909091</v>
+        <v>424.7272727272727</v>
       </c>
       <c r="C113" t="n">
-        <v>697.9242424242425</v>
+        <v>478.9242424242425</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>397.0757575757576</v>
+        <v>394.8636363636364</v>
       </c>
       <c r="B114" t="n">
+        <v>640.409090909091</v>
+      </c>
+      <c r="C114" t="n">
         <v>697.9242424242425</v>
-      </c>
-      <c r="C114" t="n">
-        <v>744.378787878788</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>402.6060606060607</v>
+        <v>397.0757575757576</v>
       </c>
       <c r="B115" t="n">
-        <v>478.9242424242425</v>
+        <v>697.9242424242425</v>
       </c>
       <c r="C115" t="n">
-        <v>530.909090909091</v>
+        <v>744.378787878788</v>
       </c>
     </row>
     <row r="116">
@@ -4491,263 +7757,263 @@
         <v>402.6060606060607</v>
       </c>
       <c r="B116" t="n">
-        <v>588.4242424242425</v>
+        <v>478.9242424242425</v>
       </c>
       <c r="C116" t="n">
-        <v>640.409090909091</v>
+        <v>530.909090909091</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>405.9242424242425</v>
+        <v>402.6060606060607</v>
       </c>
       <c r="B117" t="n">
-        <v>530.909090909091</v>
+        <v>588.4242424242425</v>
       </c>
       <c r="C117" t="n">
-        <v>588.4242424242425</v>
+        <v>640.409090909091</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>411.4545454545455</v>
+        <v>405.9242424242425</v>
       </c>
       <c r="B118" t="n">
-        <v>159.2727272727273</v>
+        <v>530.909090909091</v>
       </c>
       <c r="C118" t="n">
-        <v>214.5757575757576</v>
+        <v>588.4242424242425</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>412.5606060606061</v>
+        <v>411.4545454545455</v>
       </c>
       <c r="B119" t="n">
-        <v>744.378787878788</v>
+        <v>159.2727272727273</v>
       </c>
       <c r="C119" t="n">
-        <v>801.8939393939395</v>
+        <v>214.5757575757576</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>415.8787878787879</v>
+        <v>412.5606060606061</v>
       </c>
       <c r="B120" t="n">
-        <v>372.7424242424243</v>
+        <v>744.378787878788</v>
       </c>
       <c r="C120" t="n">
-        <v>424.7272727272727</v>
+        <v>801.8939393939395</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>420.3030303030304</v>
+        <v>415.8787878787879</v>
       </c>
       <c r="B121" t="n">
-        <v>266.5606060606061</v>
+        <v>372.7424242424243</v>
       </c>
       <c r="C121" t="n">
-        <v>319.6515151515152</v>
+        <v>424.7272727272727</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>422.5151515151516</v>
+        <v>420.3030303030304</v>
       </c>
       <c r="B122" t="n">
-        <v>424.7272727272727</v>
+        <v>266.5606060606061</v>
       </c>
       <c r="C122" t="n">
-        <v>478.9242424242425</v>
+        <v>319.6515151515152</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>429.1515151515152</v>
+        <v>422.5151515151516</v>
       </c>
       <c r="B123" t="n">
-        <v>319.6515151515152</v>
+        <v>424.7272727272727</v>
       </c>
       <c r="C123" t="n">
-        <v>372.7424242424243</v>
+        <v>478.9242424242425</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>432.469696969697</v>
+        <v>429.1515151515152</v>
       </c>
       <c r="B124" t="n">
-        <v>530.909090909091</v>
+        <v>319.6515151515152</v>
       </c>
       <c r="C124" t="n">
-        <v>588.4242424242425</v>
+        <v>372.7424242424243</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>434.6818181818182</v>
+        <v>432.469696969697</v>
       </c>
       <c r="B125" t="n">
-        <v>697.9242424242425</v>
+        <v>530.909090909091</v>
       </c>
       <c r="C125" t="n">
-        <v>744.378787878788</v>
+        <v>588.4242424242425</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>436.8939393939394</v>
+        <v>434.6818181818182</v>
       </c>
       <c r="B126" t="n">
-        <v>109.5</v>
+        <v>697.9242424242425</v>
       </c>
       <c r="C126" t="n">
-        <v>159.2727272727273</v>
+        <v>744.378787878788</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>438.0000000000001</v>
+        <v>436.8939393939394</v>
       </c>
       <c r="B127" t="n">
-        <v>478.9242424242425</v>
+        <v>109.5</v>
       </c>
       <c r="C127" t="n">
-        <v>530.909090909091</v>
+        <v>159.2727272727273</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>442.4242424242425</v>
+        <v>438.0000000000001</v>
       </c>
       <c r="B128" t="n">
-        <v>159.2727272727273</v>
+        <v>478.9242424242425</v>
       </c>
       <c r="C128" t="n">
-        <v>214.5757575757576</v>
+        <v>530.909090909091</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>446.8484848484849</v>
+        <v>442.4242424242425</v>
       </c>
       <c r="B129" t="n">
-        <v>424.7272727272727</v>
+        <v>159.2727272727273</v>
       </c>
       <c r="C129" t="n">
-        <v>478.9242424242425</v>
+        <v>214.5757575757576</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>450.1666666666667</v>
+        <v>446.8484848484849</v>
       </c>
       <c r="B130" t="n">
-        <v>214.5757575757576</v>
+        <v>424.7272727272727</v>
       </c>
       <c r="C130" t="n">
-        <v>266.5606060606061</v>
+        <v>478.9242424242425</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>452.3787878787879</v>
+        <v>450.1666666666667</v>
       </c>
       <c r="B131" t="n">
-        <v>640.409090909091</v>
+        <v>214.5757575757576</v>
       </c>
       <c r="C131" t="n">
-        <v>697.9242424242425</v>
+        <v>266.5606060606061</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>453.4848484848486</v>
+        <v>452.3787878787879</v>
       </c>
       <c r="B132" t="n">
-        <v>588.4242424242425</v>
+        <v>640.409090909091</v>
       </c>
       <c r="C132" t="n">
-        <v>640.409090909091</v>
+        <v>697.9242424242425</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>459.0151515151516</v>
+        <v>453.4848484848486</v>
       </c>
       <c r="B133" t="n">
-        <v>744.378787878788</v>
+        <v>588.4242424242425</v>
       </c>
       <c r="C133" t="n">
-        <v>801.8939393939395</v>
+        <v>640.409090909091</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>464.5454545454546</v>
+        <v>459.0151515151516</v>
       </c>
       <c r="B134" t="n">
-        <v>266.5606060606061</v>
+        <v>744.378787878788</v>
       </c>
       <c r="C134" t="n">
-        <v>319.6515151515152</v>
+        <v>801.8939393939395</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>470.0757575757576</v>
+        <v>464.5454545454546</v>
       </c>
       <c r="B135" t="n">
+        <v>266.5606060606061</v>
+      </c>
+      <c r="C135" t="n">
         <v>319.6515151515152</v>
-      </c>
-      <c r="C135" t="n">
-        <v>372.7424242424243</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>475.6060606060607</v>
+        <v>470.0757575757576</v>
       </c>
       <c r="B136" t="n">
-        <v>109.5</v>
+        <v>319.6515151515152</v>
       </c>
       <c r="C136" t="n">
-        <v>159.2727272727273</v>
+        <v>372.7424242424243</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>481.1363636363637</v>
+        <v>475.6060606060607</v>
       </c>
       <c r="B137" t="n">
-        <v>478.9242424242425</v>
+        <v>109.5</v>
       </c>
       <c r="C137" t="n">
-        <v>530.909090909091</v>
+        <v>159.2727272727273</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>499.939393939394</v>
+        <v>481.1363636363637</v>
       </c>
       <c r="B138" t="n">
-        <v>319.6515151515152</v>
+        <v>478.9242424242425</v>
       </c>
       <c r="C138" t="n">
-        <v>372.7424242424243</v>
+        <v>530.909090909091</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>501.0454545454546</v>
+        <v>499.939393939394</v>
       </c>
       <c r="B139" t="n">
-        <v>159.2727272727273</v>
+        <v>319.6515151515152</v>
       </c>
       <c r="C139" t="n">
-        <v>214.5757575757576</v>
+        <v>372.7424242424243</v>
       </c>
     </row>
     <row r="140">
@@ -4755,10 +8021,10 @@
         <v>501.0454545454546</v>
       </c>
       <c r="B140" t="n">
-        <v>266.5606060606061</v>
+        <v>159.2727272727273</v>
       </c>
       <c r="C140" t="n">
-        <v>319.6515151515152</v>
+        <v>214.5757575757576</v>
       </c>
     </row>
     <row r="141">
@@ -4766,32 +8032,32 @@
         <v>501.0454545454546</v>
       </c>
       <c r="B141" t="n">
-        <v>424.7272727272727</v>
+        <v>266.5606060606061</v>
       </c>
       <c r="C141" t="n">
-        <v>478.9242424242425</v>
+        <v>319.6515151515152</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>502.1515151515152</v>
+        <v>501.0454545454546</v>
       </c>
       <c r="B142" t="n">
-        <v>214.5757575757576</v>
+        <v>424.7272727272727</v>
       </c>
       <c r="C142" t="n">
-        <v>266.5606060606061</v>
+        <v>478.9242424242425</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>503.2575757575758</v>
+        <v>502.1515151515152</v>
       </c>
       <c r="B143" t="n">
-        <v>478.9242424242425</v>
+        <v>214.5757575757576</v>
       </c>
       <c r="C143" t="n">
-        <v>530.909090909091</v>
+        <v>266.5606060606061</v>
       </c>
     </row>
     <row r="144">
@@ -4799,10 +8065,10 @@
         <v>503.2575757575758</v>
       </c>
       <c r="B144" t="n">
-        <v>588.4242424242425</v>
+        <v>478.9242424242425</v>
       </c>
       <c r="C144" t="n">
-        <v>640.409090909091</v>
+        <v>530.909090909091</v>
       </c>
     </row>
     <row r="145">
@@ -4810,10 +8076,10 @@
         <v>503.2575757575758</v>
       </c>
       <c r="B145" t="n">
+        <v>588.4242424242425</v>
+      </c>
+      <c r="C145" t="n">
         <v>640.409090909091</v>
-      </c>
-      <c r="C145" t="n">
-        <v>697.9242424242425</v>
       </c>
     </row>
     <row r="146">
@@ -4821,10 +8087,10 @@
         <v>503.2575757575758</v>
       </c>
       <c r="B146" t="n">
+        <v>640.409090909091</v>
+      </c>
+      <c r="C146" t="n">
         <v>697.9242424242425</v>
-      </c>
-      <c r="C146" t="n">
-        <v>744.378787878788</v>
       </c>
     </row>
     <row r="147">
@@ -4832,21 +8098,21 @@
         <v>503.2575757575758</v>
       </c>
       <c r="B147" t="n">
+        <v>697.9242424242425</v>
+      </c>
+      <c r="C147" t="n">
         <v>744.378787878788</v>
-      </c>
-      <c r="C147" t="n">
-        <v>801.8939393939395</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>504.3636363636364</v>
+        <v>503.2575757575758</v>
       </c>
       <c r="B148" t="n">
-        <v>372.7424242424243</v>
+        <v>744.378787878788</v>
       </c>
       <c r="C148" t="n">
-        <v>424.7272727272727</v>
+        <v>801.8939393939395</v>
       </c>
     </row>
     <row r="149">
@@ -4854,9 +8120,20 @@
         <v>504.3636363636364</v>
       </c>
       <c r="B149" t="n">
+        <v>372.7424242424243</v>
+      </c>
+      <c r="C149" t="n">
+        <v>424.7272727272727</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>504.3636363636364</v>
+      </c>
+      <c r="B150" t="n">
         <v>530.909090909091</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C150" t="n">
         <v>588.4242424242425</v>
       </c>
     </row>
